--- a/03_Outputs/Turistica_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
@@ -16,6 +16,20 @@
     <sheet name="tti_edsup" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="internet_2025" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="uso_suelo_rural" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="_fig_01" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_fig_02" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="_fig_03" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="_fig_04" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="_fig_05" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="_fig_06" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="_fig_07" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="_fig_08" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="_fig_09" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="_fig_10" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="_fig_11" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="_fig_12" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="_fig_13" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_fig_14" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
 </workbook>
 </file>
@@ -1145,6 +1159,1752 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.259279457639503</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.288109614573427</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.302273809058651</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.310356875673876</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.356215421137737</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.367373903344619</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.686866406240968</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.438519845924853</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.715568536982615</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.704599507091162</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.337149289801486</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.417957821710222</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.0007168839960829</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.0187946087620119</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.304287966951957</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.159422521991818</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.462739600954249</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.529915488973597</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.0386012507935566</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.463856080277718</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.366844188144731</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.343234054239572</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.229657082986331</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.623257718966958</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>0.0459687419596133</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0.340703183283503</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>0.456887205473553</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>0.180649866301896</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0.300497069185951</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.0256632093782915</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.672814545279404</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>10.8929838716611</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2.98133097019221</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>8.6536073211167</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>8.3925110236849</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.611345449517688</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>7.34629832140645</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>7.41724830014554</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>6.93987335123355</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>6.06834601407636</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>16.468655986807</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>1.27365052805511</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>9.43982303627831</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Primaria</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>4.50148119296098</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Secundaria</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>1.77985280814779</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Terciaria</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>2.96064737483386</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.0433483109341502</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0114898151929753</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0414475184645883</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.0241196637077643</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.121807021017793</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.119136357963121</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.126002389621432</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.441299276716644</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.174995321313605</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.242445338401804</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.161574481669652</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.187663069737478</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.206403466810581</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.218322123375406</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>0.99060169702071</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Acueducto</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>0.820998101514742</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Alcantarillado</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0.70591734360676</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Recolección de basuras</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>0.834461940560549</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0.331808843715237</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gas natural</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0.294102998152793</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>0.992586544500931</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Acueducto</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.93579635079431</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Alcantarillado</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0.866893560801633</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Recolección de basuras</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>0.944698426552535</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Internet</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>0.601239746666835</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Gas natural</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Departamento (Antioquia)</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.66955125810138</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>serie</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Adopción TIC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>13.0181560399089</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Capacidades</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>38.6540601918846</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Dinamismo de los negocios</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>62.9410120509248</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>46.5824308656337</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Innovación</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Instituciones</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>53.5783768403641</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mercado de bienes</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>8.32937307029902</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>39.3454022202241</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>41.6677968270623</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sistema financiero</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>16.8296118866458</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Tamaño del mercado</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>20.806054873451</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Adopción TIC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>11.1355997417811</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Capacidades</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>39.8497905507535</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Dinamismo de los negocios</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>61.508126443671</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>44.8418590365667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Innovación</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Instituciones</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>49.9944215409497</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mercado de bienes</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>6.97918002835241</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Mercado laboral</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>46.8257087011245</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>45.1217806507044</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Sistema financiero</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>25.2427616863391</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tamaño del mercado</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Subregión Occidente</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>18.0573967582682</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>5.16472276562765</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>12.4549182460586</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2.30860655192213</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>14.9478905090642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>10.5150194160258</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>6.16743759621286</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>25.9343611549181</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:P11"/>
@@ -1934,6 +3694,536 @@
       </c>
       <c r="P11" s="31">
         <v>0.66955125810138</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>50.41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>23.93</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>35.37</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>54.76</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>50.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>77.79</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Gobernanza</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>71.9623830651461</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Innovación Pública Digital</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>20.0833658803312</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arquitectura</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>21.389136697391</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Seguridad y Privacidad</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>47.0526038119044</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Servicios Ciudadanos Digitales</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>40.0164197781597</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cultura y Apropiación</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>49.9566942665209</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Servicios y Procesos Inteligentes</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>13.5224633650992</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Estado Abierto</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>62.3036156850492</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Decisiones basadas en datos</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>41.5432229339166</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Proyectos de Transformación Digital</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>66.67</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ciudades y Territorios Inteligentes</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>66.4046816272386</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.285714285714286</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.411764705882353</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.294117647058824</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.290322580645161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.36986301369863</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.299270072992701</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>363.231956423059</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>589.042182048842</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>230.324797001874</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>604.803493449782</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>134.909195733641</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>174.588757695025</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>401.853366039793</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Buriticá</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.21469632591852</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ebéjico</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.0158836990173644</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.0928813559322034</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Heliconia</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.0127994748933377</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Olaya</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.0384615384615385</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sabanalarga</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.459537572254335</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>San Jerónimo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.209983722192078</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Turistica_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/03_Ordenamiento/ordenamiento.xlsx
@@ -1032,7 +1032,7 @@
         </is>
       </c>
       <c r="E3" s="112">
-        <v>0.259279457639503</v>
+        <v>0.259279457639504</v>
       </c>
     </row>
     <row r="4">
@@ -1078,7 +1078,7 @@
         </is>
       </c>
       <c r="E5" s="112">
-        <v>0.302273809058651</v>
+        <v>0.30227380905865</v>
       </c>
     </row>
     <row r="6">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.259279457639503</v>
+        <v>0.259279457639504</v>
       </c>
     </row>
     <row r="3">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.302273809058651</v>
+        <v>0.30227380905865</v>
       </c>
     </row>
     <row r="5">
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="E9" s="103">
-        <v>0.321578900855993</v>
+        <v>0.321578900855994</v>
       </c>
     </row>
   </sheetData>
